--- a/v6/files/r-content-plan.xlsx
+++ b/v6/files/r-content-plan.xlsx
@@ -485,7 +485,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3. План на 30 дней можно получить промптом из юнита «Контент под товар для соцсетей и Telegram», тексты постов промптами из набора «Промпты для соцсетей и Telegram». Факты о товарах проверьте по своим данным.</t>
+          <t>3. План на 30 дней можно получить промптом из юнита «Контент под товар для соцсетей и мессенджеров», тексты постов промптами из набора «Промпты для соцсетей и мессенджеров». Факты о товарах проверьте по своим данным.</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Типы постов: полезный, личный, продающий, закулисье, отзыв, интерактив. Ориентир из юнита «Контент под товар для соцсетей и Telegram»: продающих постов не больше 4 в месяц, интерактивных 4-5, остальное польза и истории вокруг товара.</t>
+          <t>Типы постов: полезный, личный, продающий, закулисье, отзыв, интерактив. Ориентир из юнита «Контент под товар для соцсетей и мессенджеров»: продающих постов не больше 4 в месяц, интерактивных 4-5, остальное польза и истории вокруг товара.</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>План на месяц можно получить промптом из юнита «Контент под товар для соцсетей и Telegram», тексты постов промптами из набора «Промпты для соцсетей и Telegram».</t>
+          <t>План на месяц можно получить промптом из юнита «Контент под товар для соцсетей и мессенджеров», тексты постов промптами из набора «Промпты для соцсетей и мессенджеров».</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>План на 30 постов: 9 + 4 + 4 + 4 + 4 + 5 = 30. Пропорции условные. Не больше 4 продающих и 4-5 интерактивных: ориентир из юнита «Контент под товар для соцсетей и Telegram», а не правило площадки. Подгоните под число постов, которое вам по силам.</t>
+          <t>План на 30 постов: 9 + 4 + 4 + 4 + 4 + 5 = 30. Пропорции условные. Не больше 4 продающих и 4-5 интерактивных: ориентир из юнита «Контент под товар для соцсетей и мессенджеров», а не правило площадки. Подгоните под число постов, которое вам по силам.</t>
         </is>
       </c>
     </row>

--- a/v6/files/r-content-plan.xlsx
+++ b/v6/files/r-content-plan.xlsx
@@ -485,7 +485,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3. План на 30 дней можно получить промптом из юнита «Контент под товар для соцсетей и мессенджеров», тексты постов промптами из набора «Промпты для соцсетей и мессенджеров». Факты о товарах проверьте по своим данным.</t>
+          <t>3. План на 30 дней можно получить промптом из задания «Контент под товар для соцсетей и мессенджеров», тексты постов промптами из набора «Промпты для соцсетей и мессенджеров». Факты о товарах проверьте по своим данным.</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Типы постов: полезный, личный, продающий, закулисье, отзыв, интерактив. Ориентир из юнита «Контент под товар для соцсетей и мессенджеров»: продающих постов не больше 4 в месяц, интерактивных 4-5, остальное польза и истории вокруг товара.</t>
+          <t>Типы постов: полезный, личный, продающий, закулисье, отзыв, интерактив. Ориентир из задания «Контент под товар для соцсетей и мессенджеров»: продающих постов не больше 4 в месяц, интерактивных 4-5, остальное польза и истории вокруг товара.</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>План на месяц можно получить промптом из юнита «Контент под товар для соцсетей и мессенджеров», тексты постов промптами из набора «Промпты для соцсетей и мессенджеров».</t>
+          <t>План на месяц можно получить промптом из задания «Контент под товар для соцсетей и мессенджеров», тексты постов промптами из набора «Промпты для соцсетей и мессенджеров».</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>План на 30 постов: 9 + 4 + 4 + 4 + 4 + 5 = 30. Пропорции условные. Не больше 4 продающих и 4-5 интерактивных: ориентир из юнита «Контент под товар для соцсетей и мессенджеров», а не правило площадки. Подгоните под число постов, которое вам по силам.</t>
+          <t>План на 30 постов: 9 + 4 + 4 + 4 + 4 + 5 = 30. Пропорции условные. Не больше 4 продающих и 4-5 интерактивных: ориентир из задания «Контент под товар для соцсетей и мессенджеров», а не правило площадки. Подгоните под число постов, которое вам по силам.</t>
         </is>
       </c>
     </row>
